--- a/港岛-筲箕湾-One Eighty/One Eighty_销控明细表.xlsx
+++ b/港岛-筲箕湾-One Eighty/One Eighty_销控明细表.xlsx
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2019-11-27</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2020-06-17</t>
+          <t>2020-06-18</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2020-02-11</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2019-11-27</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2019-11-27</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2019-11-27</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2019-11-29</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019-11-26</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2019-11-20</t>
+          <t>2019-11-21</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2019-11-22</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2019-11-22</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2019-11-22</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2019-11-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2019-11-24</t>
+          <t>2019-11-25</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2019-11-21</t>
+          <t>2019-11-22</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4539,7 +4539,7 @@
           <t>A | 331呎 (2房)
 $859万
 $25,963/呎
-(19年-11月-27日)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -4563,7 +4563,7 @@
           <t>A | 331呎 (2房)
 $843万
 $25,472/呎
-(20年-06月-17日)</t>
+(20年-06月-18日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -4587,7 +4587,7 @@
           <t>A | 253呎 (1房)
 $660万
 $26,084/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -4595,7 +4595,7 @@
           <t>B | 165呎 (开放式)
 $436万
 $26,424/呎
-(19年-11月-28日)</t>
+(19年-11月-29日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -4603,7 +4603,7 @@
           <t>C | 247呎 (1房)
 $645万
 $26,094/呎
-(20年-02月-11日)</t>
+(20年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
           <t>A | 253呎 (1房)
 $633万
 $25,011/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -4626,7 +4626,7 @@
           <t>B | 164呎 (开放式)
 $418万
 $25,495/呎
-(19年-11月-28日)</t>
+(19年-11月-29日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -4634,7 +4634,7 @@
           <t>C | 248呎 (1房)
 $618万
 $24,921/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
           <t>A | 253呎 (1房)
 $643万
 $25,410/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -4657,7 +4657,7 @@
           <t>B | 164呎 (开放式)
 $425万
 $25,940/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -4665,7 +4665,7 @@
           <t>C | 248呎 (1房)
 $627万
 $25,274/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
           <t>A | 253呎 (1房)
 $618万
 $24,422/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -4688,7 +4688,7 @@
           <t>B | 165呎 (开放式)
 $399万
 $24,187/呎
-(19年-11月-27日)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -4696,7 +4696,7 @@
           <t>C | 247呎 (1房)
 $612万
 $24,766/呎
-(19年-11月-27日)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
           <t>A | 253呎 (1房)
 $596万
 $23,540/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -4719,7 +4719,7 @@
           <t>B | 164呎 (开放式)
 $394万
 $24,025/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -4727,7 +4727,7 @@
           <t>C | 248呎 (1房)
 $586万
 $23,631/呎
-(19年-11月-28日)</t>
+(19年-11月-29日)</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
           <t>A | 253呎 (1房)
 $591万
 $23,362/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -4750,7 +4750,7 @@
           <t>B | 165呎 (开放式)
 $389万
 $23,566/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -4758,7 +4758,7 @@
           <t>C | 247呎 (1房)
 $578万
 $23,415/呎
-(19年-11月-27日)</t>
+(19年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
           <t>A | 253呎 (1房)
 $614万
 $24,256/呎
-(19年-11月-28日)</t>
+(19年-11月-29日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -4781,7 +4781,7 @@
           <t>B | 165呎 (开放式)
 $403万
 $24,416/呎
-(20年-07月-02日)</t>
+(20年-07月-03日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -4789,7 +4789,7 @@
           <t>C | 248呎 (1房)
 $599万
 $24,157/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
           <t>A | 253呎 (1房)
 $577万
 $22,791/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -4812,7 +4812,7 @@
           <t>B | 164呎 (开放式)
 $379万
 $23,080/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -4820,7 +4820,7 @@
           <t>C | 247呎 (1房)
 $563万
 $22,787/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
           <t>A | 253呎 (1房)
 $569万
 $22,474/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -4843,7 +4843,7 @@
           <t>B | 164呎 (开放式)
 $373万
 $22,770/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -4851,7 +4851,7 @@
           <t>C | 247呎 (1房)
 $555万
 $22,472/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
           <t>A | 253呎 (1房)
 $589万
 $23,268/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -4874,7 +4874,7 @@
           <t>B | 164呎 (开放式)
 $368万
 $22,455/呎
-(19年-11月-25日)</t>
+(19年-11月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -4882,7 +4882,7 @@
           <t>C | 247呎 (1房)
 $575万
 $23,268/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
           <t>A | 253呎 (1房)
 $580万
 $22,937/呎
-(19年-11月-20日)</t>
+(19年-11月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -4905,7 +4905,7 @@
           <t>B | 165呎 (开放式)
 $381万
 $23,109/呎
-(19年-11月-26日)</t>
+(19年-11月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -4913,7 +4913,7 @@
           <t>C | 248呎 (1房)
 $544万
 $21,931/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
           <t>A | 253呎 (1房)
 $545万
 $21,534/呎
-(19年-11月-21日)</t>
+(19年-11月-22日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -4936,7 +4936,7 @@
           <t>B | 165呎 (开放式)
 $358万
 $21,693/呎
-(19年-11月-21日)</t>
+(19年-11月-22日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -4944,7 +4944,7 @@
           <t>C | 248呎 (1房)
 $511万
 $20,589/呎
-(19年-11月-21日)</t>
+(19年-11月-22日)</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
           <t>A | 253呎 (1房)
 $536万
 $21,200/呎
-(19年-11月-21日)</t>
+(19年-11月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -4967,7 +4967,7 @@
           <t>B | 164呎 (开放式)
 $353万
 $21,515/呎
-(19年-11月-24日)</t>
+(19年-11月-25日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -4975,7 +4975,7 @@
           <t>C | 248呎 (1房)
 $503万
 $20,269/呎
-(19年-11月-21日)</t>
+(19年-11月-22日)</t>
         </is>
       </c>
     </row>
